--- a/data/trans_camb/P2C_R2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R2-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,39; 19,09</t>
+          <t>2,84; 19,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 11,93</t>
+          <t>-5,27; 11,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-34,89; -22,36</t>
+          <t>-35,55; -22,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,79; 21,67</t>
+          <t>3,67; 21,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 6,78</t>
+          <t>-10,34; 6,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-41,97; -28,15</t>
+          <t>-41,37; -28,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,48; 19,08</t>
+          <t>5,61; 17,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 6,54</t>
+          <t>-5,05; 7,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-36,41; -26,99</t>
+          <t>-36,1; -26,76</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,09; 63,65</t>
+          <t>7,49; 64,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 39,15</t>
+          <t>-13,49; 37,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-89,8; -73,57</t>
+          <t>-89,52; -73,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,73; 56,23</t>
+          <t>7,47; 55,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-22,11; 17,55</t>
+          <t>-21,06; 16,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-85,7; -72,51</t>
+          <t>-86,11; -73,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,92; 53,17</t>
+          <t>13,48; 49,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-12,73; 18,1</t>
+          <t>-11,96; 19,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-86,02; -76,31</t>
+          <t>-85,89; -75,57</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,46; 27,91</t>
+          <t>16,15; 28,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 9,07</t>
+          <t>-2,46; 8,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,35; -7,28</t>
+          <t>-17,04; -7,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,57; 25,66</t>
+          <t>12,95; 25,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 9,21</t>
+          <t>-3,12; 9,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,39; -6,02</t>
+          <t>-16,28; -6,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,85; 25,01</t>
+          <t>16,74; 25,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 7,47</t>
+          <t>-0,65; 7,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-15,27; -8,17</t>
+          <t>-15,83; -8,82</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>60,02; 138,42</t>
+          <t>62,29; 140,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 44,91</t>
+          <t>-9,31; 44,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-67,64; -35,51</t>
+          <t>-66,49; -34,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40,07; 92,43</t>
+          <t>37,83; 91,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 32,78</t>
+          <t>-9,01; 35,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-48,27; -21,09</t>
+          <t>-48,25; -21,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,56; 101,09</t>
+          <t>57,45; 102,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 30,04</t>
+          <t>-2,43; 30,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-52,81; -32,78</t>
+          <t>-53,49; -33,95</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,9; 18,32</t>
+          <t>3,46; 18,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,91; -0,62</t>
+          <t>-14,84; -0,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-28,41; -15,45</t>
+          <t>-28,57; -16,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,68; 22,51</t>
+          <t>7,89; 23,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 1,89</t>
+          <t>-12,56; 2,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-28,63; -16,87</t>
+          <t>-28,64; -16,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,85; 18,71</t>
+          <t>7,61; 18,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,3; -1,59</t>
+          <t>-11,43; -1,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-26,83; -17,76</t>
+          <t>-26,32; -17,77</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,57; 61,36</t>
+          <t>9,14; 61,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-39,4; -2,22</t>
+          <t>-39,54; -2,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-74,64; -49,23</t>
+          <t>-74,05; -52,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19,14; 69,92</t>
+          <t>21,5; 74,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-31,76; 6,03</t>
+          <t>-31,76; 6,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-71,96; -52,7</t>
+          <t>-71,92; -50,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,42; 59,17</t>
+          <t>20,54; 57,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-30,09; -4,66</t>
+          <t>-30,84; -4,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-71,13; -55,16</t>
+          <t>-69,84; -54,59</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13,14; 27,84</t>
+          <t>13,62; 27,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 7,48</t>
+          <t>-6,03; 8,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-20,74; -6,49</t>
+          <t>-19,7; -6,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,83; 24,79</t>
+          <t>10,24; 24,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 8,31</t>
+          <t>-6,33; 8,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-31,99; -18,78</t>
+          <t>-32,34; -18,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,01; 24,48</t>
+          <t>14,25; 24,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 6,21</t>
+          <t>-3,65; 5,97</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-25,47; -14,97</t>
+          <t>-25,39; -15,29</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>39,98; 110,42</t>
+          <t>39,65; 111,47</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-17,58; 28,9</t>
+          <t>-17,99; 33,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-64,18; -25,26</t>
+          <t>-61,72; -22,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23,62; 72,47</t>
+          <t>24,35; 70,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-13,57; 24,45</t>
+          <t>-14,7; 25,44</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-78,66; -53,35</t>
+          <t>-78,78; -52,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,43; 79,03</t>
+          <t>38,93; 75,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,45; 19,71</t>
+          <t>-10,26; 19,04</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-70,64; -47,28</t>
+          <t>-70,74; -48,16</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12,84; 32,77</t>
+          <t>14,58; 33,2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9,84; 27,94</t>
+          <t>10,25; 28,22</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-19,23; -5,38</t>
+          <t>-19,06; -4,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16,54; 35,35</t>
+          <t>16,71; 34,76</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,24; 25,68</t>
+          <t>6,9; 25,56</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-29,52; -13,81</t>
+          <t>-29,59; -14,28</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,59; 31,35</t>
+          <t>18,86; 31,67</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11,87; 23,96</t>
+          <t>11,61; 24,72</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-22,02; -11,98</t>
+          <t>-22,16; -11,86</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>43,48; 171,5</t>
+          <t>51,16; 172,89</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>35,48; 149,48</t>
+          <t>36,8; 150,75</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-70,19; -28,19</t>
+          <t>-70,49; -21,45</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>46,88; 138,07</t>
+          <t>45,88; 132,44</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>18,84; 100,04</t>
+          <t>20,31; 101,13</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-84,16; -54,19</t>
+          <t>-83,65; -54,63</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>62,64; 132,64</t>
+          <t>63,48; 134,45</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>39,0; 101,52</t>
+          <t>37,95; 104,79</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-75,15; -51,32</t>
+          <t>-74,9; -49,96</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>1,81; 17,99</t>
+          <t>1,41; 18,09</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 2,87</t>
+          <t>-13,64; 2,61</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-24,52; -10,77</t>
+          <t>-24,65; -10,74</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13,59; 28,95</t>
+          <t>12,69; 29,3</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 12,14</t>
+          <t>-4,29; 11,96</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-12,73; 1,35</t>
+          <t>-12,62; 1,92</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,64; 21,45</t>
+          <t>9,5; 21,99</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 4,1</t>
+          <t>-6,24; 4,96</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-16,75; -6,71</t>
+          <t>-16,7; -6,46</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>4,54; 57,04</t>
+          <t>3,76; 59,6</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-34,52; 10,13</t>
+          <t>-35,86; 7,91</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-61,93; -33,27</t>
+          <t>-62,78; -34,78</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>41,41; 117,68</t>
+          <t>36,39; 117,32</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-13,17; 49,4</t>
+          <t>-13,1; 45,77</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-37,71; 6,12</t>
+          <t>-36,25; 9,92</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>27,04; 71,23</t>
+          <t>26,84; 75,97</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-19,01; 13,93</t>
+          <t>-17,83; 16,97</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-47,7; -22,41</t>
+          <t>-47,33; -22,23</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>10,09; 20,61</t>
+          <t>9,22; 20,45</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 2,72</t>
+          <t>-7,99; 2,94</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-27,64; -18,44</t>
+          <t>-27,94; -19,53</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4,37; 15,12</t>
+          <t>3,79; 15,01</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 3,02</t>
+          <t>-8,15; 2,84</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-32,98; 22,28</t>
+          <t>-33,38; 27,12</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,23; 16,21</t>
+          <t>8,75; 16,55</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 1,07</t>
+          <t>-6,41; 0,9</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-28,85; 16,22</t>
+          <t>-28,85; 13,93</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>31,25; 78,19</t>
+          <t>28,95; 77,85</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-23,1; 10,18</t>
+          <t>-25,25; 11,17</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-87,53; -70,72</t>
+          <t>-87,51; -72,46</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>10,24; 41,69</t>
+          <t>9,02; 42,39</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-18,7; 8,54</t>
+          <t>-19,38; 7,88</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-82,82; 60,28</t>
+          <t>-82,85; 73,08</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,42; 50,0</t>
+          <t>24,28; 51,95</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-17,21; 3,51</t>
+          <t>-18,2; 2,66</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-82,91; 49,32</t>
+          <t>-83,09; 42,55</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>7,76; 17,59</t>
+          <t>7,97; 18,52</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2,76; 11,76</t>
+          <t>2,26; 11,95</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-23,69; -5,18</t>
+          <t>-23,95; -5,31</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>14,73; 24,4</t>
+          <t>14,9; 24,67</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>9,82; 19,64</t>
+          <t>9,33; 18,84</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 4,67</t>
+          <t>-4,43; 4,32</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>12,91; 19,63</t>
+          <t>12,73; 19,78</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>7,55; 14,48</t>
+          <t>7,62; 14,16</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-16,8; -2,2</t>
+          <t>-15,48; -1,85</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>24,19; 65,77</t>
+          <t>25,55; 69,87</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>8,57; 44,91</t>
+          <t>7,22; 45,57</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-74,58; -18,43</t>
+          <t>-75,6; -18,17</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>44,13; 86,38</t>
+          <t>44,28; 87,85</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>29,52; 69,05</t>
+          <t>28,35; 67,52</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 16,56</t>
+          <t>-13,66; 15,54</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>40,91; 70,08</t>
+          <t>41,0; 70,51</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>23,28; 51,47</t>
+          <t>24,5; 51,63</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-53,89; -7,54</t>
+          <t>-51,93; -6,54</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>13,19; 17,96</t>
+          <t>13,2; 17,91</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 4,29</t>
+          <t>-0,05; 4,53</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-20,26; -15,32</t>
+          <t>-19,94; -14,99</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>14,81; 19,48</t>
+          <t>14,8; 19,41</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,01; 6,67</t>
+          <t>1,87; 6,83</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-18,38; 2,2</t>
+          <t>-18,47; 1,43</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>14,47; 18,06</t>
+          <t>14,74; 18,19</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,92</t>
+          <t>1,56; 4,89</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-18,13; -6,23</t>
+          <t>-18,07; -8,1</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>42,97; 63,68</t>
+          <t>43,88; 64,65</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 15,29</t>
+          <t>-0,09; 16,13</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-67,55; -53,93</t>
+          <t>-67,86; -53,66</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>40,97; 58,15</t>
+          <t>41,2; 57,95</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>5,62; 20,09</t>
+          <t>5,14; 20,41</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-52,56; 6,55</t>
+          <t>-52,76; 4,24</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>44,71; 58,58</t>
+          <t>44,76; 58,34</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>4,83; 15,87</t>
+          <t>4,8; 15,76</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-56,45; -19,62</t>
+          <t>-56,4; -25,65</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R2-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-28,89</t>
+          <t>-28,92</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-34,6</t>
+          <t>-34,07</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-31,7</t>
+          <t>-31,41</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,84; 19,24</t>
+          <t>1,65; 18,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 11,55</t>
+          <t>-5,23; 11,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-35,55; -22,76</t>
+          <t>-35,02; -23,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,67; 21,41</t>
+          <t>3,79; 21,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 6,47</t>
+          <t>-9,69; 7,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-41,37; -28,0</t>
+          <t>-41,12; -27,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,61; 17,47</t>
+          <t>5,65; 18,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 7,07</t>
+          <t>-5,03; 7,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-36,1; -26,76</t>
+          <t>-36,42; -26,78</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-83,17%</t>
+          <t>-83,25%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-80,2%</t>
+          <t>-78,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-81,61%</t>
+          <t>-80,85%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,49; 64,49</t>
+          <t>4,37; 59,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,49; 37,06</t>
+          <t>-13,76; 36,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-89,52; -73,5</t>
+          <t>-89,7; -74,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,47; 55,57</t>
+          <t>8,01; 54,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-21,06; 16,73</t>
+          <t>-20,69; 19,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-86,11; -73,14</t>
+          <t>-85,03; -71,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,48; 49,09</t>
+          <t>13,3; 51,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 19,39</t>
+          <t>-12,0; 20,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-85,89; -75,57</t>
+          <t>-85,29; -75,04</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-12,25</t>
+          <t>-11,24</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-11,13</t>
+          <t>-10,17</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-11,75</t>
+          <t>-10,68</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,15; 28,11</t>
+          <t>15,9; 27,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 8,85</t>
+          <t>-2,54; 9,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,04; -7,23</t>
+          <t>-16,78; -6,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,95; 25,49</t>
+          <t>13,74; 25,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 9,67</t>
+          <t>-2,4; 8,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,28; -6,03</t>
+          <t>-15,67; -4,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,74; 25,13</t>
+          <t>16,14; 24,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 7,44</t>
+          <t>-0,41; 7,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-15,83; -8,82</t>
+          <t>-14,49; -7,27</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-53,22%</t>
+          <t>-48,81%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-36,13%</t>
+          <t>-33,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-43,58%</t>
+          <t>-39,63%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>62,29; 140,57</t>
+          <t>61,64; 139,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 44,04</t>
+          <t>-9,74; 46,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-66,49; -34,4</t>
+          <t>-64,71; -30,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37,83; 91,11</t>
+          <t>41,34; 93,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 35,9</t>
+          <t>-7,12; 31,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-48,25; -21,54</t>
+          <t>-46,52; -17,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,45; 102,07</t>
+          <t>55,02; 99,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 30,05</t>
+          <t>-1,46; 29,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-53,49; -33,95</t>
+          <t>-49,24; -28,1</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-22,06</t>
+          <t>-21,71</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-22,49</t>
+          <t>-22,91</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-22,26</t>
+          <t>-22,32</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,46; 18,81</t>
+          <t>2,58; 18,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,84; -0,63</t>
+          <t>-15,11; -1,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-28,57; -16,56</t>
+          <t>-28,1; -15,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,89; 23,47</t>
+          <t>7,96; 22,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,56; 2,04</t>
+          <t>-12,98; 1,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-28,64; -16,3</t>
+          <t>-28,44; -16,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,61; 18,42</t>
+          <t>8,14; 18,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,43; -1,34</t>
+          <t>-11,35; -1,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-26,32; -17,77</t>
+          <t>-26,62; -18,08</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-64,72%</t>
+          <t>-63,7%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-62,92%</t>
+          <t>-64,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-63,73%</t>
+          <t>-63,89%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,14; 61,44</t>
+          <t>6,66; 60,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-39,54; -2,08</t>
+          <t>-39,83; -3,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-74,05; -52,83</t>
+          <t>-74,72; -50,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21,5; 74,5</t>
+          <t>19,45; 69,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-31,76; 6,05</t>
+          <t>-32,87; 4,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-71,92; -50,95</t>
+          <t>-72,07; -52,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,54; 57,72</t>
+          <t>21,51; 57,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-30,84; -4,07</t>
+          <t>-30,06; -4,48</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-69,84; -54,59</t>
+          <t>-71,34; -56,49</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-13,48</t>
+          <t>-12,66</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-25,15</t>
+          <t>-21,29</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-19,64</t>
+          <t>-17,04</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13,62; 27,81</t>
+          <t>13,28; 28,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 8,18</t>
+          <t>-5,61; 7,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-19,7; -6,68</t>
+          <t>-20,0; -5,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,24; 24,47</t>
+          <t>10,79; 23,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 8,49</t>
+          <t>-6,26; 8,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-32,34; -18,88</t>
+          <t>-27,19; -15,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,25; 24,14</t>
+          <t>13,95; 24,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 5,97</t>
+          <t>-3,89; 6,35</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-25,39; -15,29</t>
+          <t>-21,86; -12,57</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-46,41%</t>
+          <t>-43,59%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-65,58%</t>
+          <t>-55,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-58,15%</t>
+          <t>-50,44%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>39,65; 111,47</t>
+          <t>40,59; 111,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-17,99; 33,25</t>
+          <t>-17,69; 29,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-61,72; -22,8</t>
+          <t>-61,33; -22,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24,35; 70,53</t>
+          <t>25,15; 68,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-14,7; 25,44</t>
+          <t>-15,32; 22,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-78,78; -52,65</t>
+          <t>-65,07; -44,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,93; 75,86</t>
+          <t>38,17; 77,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 19,04</t>
+          <t>-10,56; 20,28</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-70,74; -48,16</t>
+          <t>-60,02; -40,13</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-12,5</t>
+          <t>-12,0</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-21,03</t>
+          <t>-18,5</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-16,93</t>
+          <t>-15,27</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14,58; 33,2</t>
+          <t>15,74; 34,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10,25; 28,22</t>
+          <t>10,32; 28,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-19,06; -4,29</t>
+          <t>-19,45; -5,01</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16,71; 34,76</t>
+          <t>16,52; 35,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,9; 25,56</t>
+          <t>7,74; 25,64</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-29,59; -14,28</t>
+          <t>-25,97; -12,03</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,86; 31,67</t>
+          <t>18,63; 30,95</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11,61; 24,72</t>
+          <t>12,02; 24,37</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-22,16; -11,86</t>
+          <t>-20,09; -10,23</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-53,67%</t>
+          <t>-51,51%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-69,09%</t>
+          <t>-60,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-62,93%</t>
+          <t>-56,76%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>51,16; 172,89</t>
+          <t>55,27; 187,06</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>36,8; 150,75</t>
+          <t>36,7; 143,88</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-70,49; -21,45</t>
+          <t>-69,16; -21,43</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45,88; 132,44</t>
+          <t>45,77; 137,68</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>20,31; 101,13</t>
+          <t>21,48; 100,57</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-83,65; -54,63</t>
+          <t>-71,94; -46,71</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>63,48; 134,45</t>
+          <t>62,28; 130,59</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>37,95; 104,79</t>
+          <t>39,32; 100,67</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-74,9; -49,96</t>
+          <t>-67,19; -44,16</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-17,45</t>
+          <t>-16,85</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-5,76</t>
+          <t>-5,73</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-11,64</t>
+          <t>-11,28</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>1,41; 18,09</t>
+          <t>1,12; 18,76</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-13,64; 2,61</t>
+          <t>-13,71; 2,66</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-24,65; -10,74</t>
+          <t>-24,03; -10,01</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12,69; 29,3</t>
+          <t>13,55; 30,33</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 11,96</t>
+          <t>-4,61; 11,82</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 1,92</t>
+          <t>-12,66; 1,08</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,5; 21,99</t>
+          <t>9,61; 21,64</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 4,96</t>
+          <t>-6,66; 4,77</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-16,7; -6,46</t>
+          <t>-16,2; -6,16</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-49,66%</t>
+          <t>-47,96%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-19,58%</t>
+          <t>-19,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-36,09%</t>
+          <t>-34,99%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3,76; 59,6</t>
+          <t>2,75; 61,24</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-35,86; 7,91</t>
+          <t>-35,31; 8,6</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-62,78; -34,78</t>
+          <t>-60,93; -31,68</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>36,39; 117,32</t>
+          <t>40,35; 120,96</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 45,77</t>
+          <t>-13,95; 44,67</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-36,25; 9,92</t>
+          <t>-37,96; 4,49</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>26,84; 75,97</t>
+          <t>27,48; 74,6</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-17,83; 16,97</t>
+          <t>-19,42; 16,12</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-47,33; -22,23</t>
+          <t>-45,34; -20,13</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-23,53</t>
+          <t>-23,13</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-9,56</t>
+          <t>-30,95</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-14,79</t>
+          <t>-27,09</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>9,22; 20,45</t>
+          <t>10,04; 21,33</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 2,94</t>
+          <t>-7,76; 2,91</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-27,94; -19,53</t>
+          <t>-27,2; -19,15</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,79; 15,01</t>
+          <t>4,09; 14,91</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 2,84</t>
+          <t>-8,43; 2,74</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-33,38; 27,12</t>
+          <t>-34,98; -26,5</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,75; 16,55</t>
+          <t>8,2; 16,19</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 0,9</t>
+          <t>-6,2; 1,35</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-28,85; 13,93</t>
+          <t>-30,17; -24,04</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-81,56%</t>
+          <t>-80,16%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-24,41%</t>
+          <t>-79,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-43,36%</t>
+          <t>-79,42%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>28,95; 77,85</t>
+          <t>31,45; 83,66</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-25,25; 11,17</t>
+          <t>-24,21; 10,96</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-87,51; -72,46</t>
+          <t>-86,47; -72,16</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9,02; 42,39</t>
+          <t>9,78; 41,02</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-19,38; 7,88</t>
+          <t>-19,98; 7,57</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-82,85; 73,08</t>
+          <t>-83,48; -73,34</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24,28; 51,95</t>
+          <t>22,95; 50,98</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-18,2; 2,66</t>
+          <t>-17,26; 4,13</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-83,09; 42,55</t>
+          <t>-83,5; -74,84</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-12,44</t>
+          <t>-5,8</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,01</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-7,17</t>
+          <t>-2,55</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>7,97; 18,52</t>
+          <t>7,97; 17,8</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2,26; 11,95</t>
+          <t>2,34; 11,95</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-23,95; -5,31</t>
+          <t>-10,21; -1,13</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>14,9; 24,67</t>
+          <t>14,33; 24,49</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>9,33; 18,84</t>
+          <t>9,63; 19,25</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 4,32</t>
+          <t>-3,81; 5,25</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>12,73; 19,78</t>
+          <t>12,85; 19,69</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>7,62; 14,16</t>
+          <t>7,71; 14,35</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-15,48; -1,85</t>
+          <t>-5,82; 0,89</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-43,17%</t>
+          <t>-20,14%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-24,01%</t>
+          <t>-8,55%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>25,55; 69,87</t>
+          <t>24,59; 67,03</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>7,22; 45,57</t>
+          <t>7,29; 45,16</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-75,6; -18,17</t>
+          <t>-32,92; -4,62</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>44,28; 87,85</t>
+          <t>42,39; 86,6</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>28,35; 67,52</t>
+          <t>28,89; 66,89</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-13,66; 15,54</t>
+          <t>-11,3; 18,85</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>41,0; 70,51</t>
+          <t>40,01; 70,01</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>24,5; 51,63</t>
+          <t>23,93; 50,6</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-51,93; -6,54</t>
+          <t>-18,63; 3,13</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-17,22</t>
+          <t>-15,6</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-13,16</t>
+          <t>-16,5</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-15,07</t>
+          <t>-16,03</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>13,2; 17,91</t>
+          <t>13,37; 17,95</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 4,53</t>
+          <t>-0,15; 4,51</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-19,94; -14,99</t>
+          <t>-17,47; -13,52</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>14,8; 19,41</t>
+          <t>14,45; 19,47</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,87; 6,83</t>
+          <t>1,73; 6,38</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-18,47; 1,43</t>
+          <t>-18,44; -14,41</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>14,74; 18,19</t>
+          <t>14,77; 18,16</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,89</t>
+          <t>1,38; 4,67</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-18,07; -8,1</t>
+          <t>-17,53; -14,72</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-59,07%</t>
+          <t>-53,51%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-38,12%</t>
+          <t>-47,79%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-47,26%</t>
+          <t>-50,28%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>43,88; 64,65</t>
+          <t>44,03; 63,77</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 16,13</t>
+          <t>-0,46; 16,23</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-67,86; -53,66</t>
+          <t>-58,05; -48,38</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>41,2; 57,95</t>
+          <t>40,18; 57,83</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>5,14; 20,41</t>
+          <t>4,78; 19,03</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-52,76; 4,24</t>
+          <t>-51,72; -42,9</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>44,76; 58,34</t>
+          <t>45,14; 58,5</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>4,8; 15,76</t>
+          <t>3,98; 14,9</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-56,4; -25,65</t>
+          <t>-53,51; -47,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R2-Provincia-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son no remunerados</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
